--- a/AAII_Financials/Yearly/LOT_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/LOT_YR_FIN.xlsx
@@ -2272,10 +2272,10 @@
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>722600</v>
+        <v>566100</v>
       </c>
       <c r="E57" s="3">
-        <v>681800</v>
+        <v>497700</v>
       </c>
       <c r="F57" s="3">
         <v>605500</v>
@@ -2344,10 +2344,10 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>93400</v>
+        <v>249800</v>
       </c>
       <c r="E59" s="3">
-        <v>579600</v>
+        <v>763800</v>
       </c>
       <c r="F59" s="3">
         <v>235500</v>
